--- a/owlcms/src/main/resources/templates/protocol/PanAmProtocol-A4.xlsx
+++ b/owlcms/src/main/resources/templates/protocol/PanAmProtocol-A4.xlsx
@@ -444,7 +444,7 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" ns1:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ns1="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:ns2="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:ns3="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:ns4="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:ns5="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" ns1:Ignorable="x14ac x16r2 xr">
   <numFmts count="6">
     <numFmt numFmtId="164" formatCode="0.0;;"/>
     <numFmt numFmtId="165" formatCode="_ * #,##0_)\ _$_ ;_ * \(#,##0&quot;) &quot;_$_ ;_ * \-??_)\ _$_ ;_ @_ "/>
@@ -1521,358 +1521,358 @@
       <left/>
       <right/>
       <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -1880,8 +1880,8 @@
       <top style="thin">
         <color indexed="8"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -1889,8 +1889,8 @@
       <top style="thin">
         <color indexed="8"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -1898,50 +1898,50 @@
       <top style="thin">
         <color indexed="8"/>
       </top>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -1949,8 +1949,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -1958,8 +1958,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -1967,8 +1967,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -1976,8 +1976,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -1985,8 +1985,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -1994,8 +1994,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2003,8 +2003,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2012,8 +2012,8 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
     </border>
     <border>
       <left/>
@@ -2021,71 +2021,71 @@
       <top style="thin">
         <color indexed="64"/>
       </top>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <diagonal/>
-      <bottom/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom/>
+      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="19">
@@ -2530,16 +2530,16 @@
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
     </xf>
     <xf numFmtId="49" fontId="56" fillId="0" borderId="48" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
       <protection locked="0"/>
-      <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
     </xf>
     <xf numFmtId="49" fontId="57" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
       <protection locked="0"/>
-      <alignment horizontal="right" vertical="center" wrapText="1" shrinkToFit="0"/>
     </xf>
     <xf numFmtId="49" fontId="58" fillId="0" borderId="50" xfId="0" applyNumberFormat="1" applyBorder="1" applyProtection="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
       <protection locked="0"/>
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
     </xf>
     <xf numFmtId="0" fontId="59" fillId="0" borderId="51" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" shrinkToFit="0"/>
@@ -2708,8 +2708,8 @@
       <protection locked="0"/>
     </xf>
     <xf numFmtId="49" fontId="58" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="0" applyProtection="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
       <protection locked="0"/>
-      <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
     </xf>
     <xf numFmtId="0" fontId="76" fillId="0" borderId="0" xfId="0" applyAlignment="1" applyBorder="0">
       <alignment horizontal="left" vertical="center" wrapText="1" shrinkToFit="0"/>
@@ -4206,21 +4206,6 @@
     <mergeCell ref="A4:C4"/>
     <mergeCell ref="D4:V4"/>
   </mergeCells>
-  <conditionalFormatting sqref="C8:D8">
-    <cfRule type="expression" dxfId="2" priority="7" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D10:E10">
-    <cfRule type="expression" dxfId="1" priority="11" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="D11:F13">
-    <cfRule type="expression" dxfId="0" priority="5" stopIfTrue="1">
-      <formula>AND((#REF!),#REF!,#REF!)</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="4">
     <dataValidation showErrorMessage="1" sqref="K4 F23 C20 S18 S23 F20 C23 L20 S20 C17 L17 F18" ns1:uid="{00000000-0002-0000-0000-000000000000}"/>
     <dataValidation allowBlank="1" showErrorMessage="1" sqref="H10" ns1:uid="{00000000-0002-0000-0000-000001000000}"/>
@@ -4233,7 +4218,6 @@
       <formula2>200</formula2>
     </dataValidation>
   </dataValidations>
-  <hyperlinks/>
   <pageMargins left="0.31496062992125984" right="0.35433070866141736" top="0.39370078740157483" bottom="0.39370078740157483" header="0.51181102362204722" footer="0.31496062992125984"/>
   <pageSetup paperSize="9" scale="70" firstPageNumber="0" fitToHeight="0" orientation="landscape" horizontalDpi="300" verticalDpi="300" ns3:id="rId3"/>
   <headerFooter alignWithMargins="0"/>
